--- a/docs/Arbeitsrapport.xlsx
+++ b/docs/Arbeitsrapport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brtoz\Codes\IPT5.1\Stundenplaner-Projekt\IPT5.1_Stundenplaner-Projekt\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B24C715-F276-46F0-8FC4-CF96E5F6246E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08AD5BB-442D-4663-A76B-39792E97A105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2676" yWindow="2508" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Sales Report Form" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="91">
   <si>
     <t>Datum</t>
   </si>
@@ -261,6 +261,51 @@
   </si>
   <si>
     <t>1 Sekunde</t>
+  </si>
+  <si>
+    <t>Sanjivan, Kenan, Berat</t>
+  </si>
+  <si>
+    <t>Canvas Übertragung Verbesserung</t>
+  </si>
+  <si>
+    <t>Da Halldor seine Aufgabe nicht gut gemacht hat, mussten die Restlichen Alles verbessern.</t>
+  </si>
+  <si>
+    <t>Sanjivan, Berat, Kenan</t>
+  </si>
+  <si>
+    <t>MSTests</t>
+  </si>
+  <si>
+    <t>Anfang UnitTests</t>
+  </si>
+  <si>
+    <t>UnitTests/Bugfixes</t>
+  </si>
+  <si>
+    <t>Implementation Strategy Pattern</t>
+  </si>
+  <si>
+    <t>UnitTests für Valuation</t>
+  </si>
+  <si>
+    <t>Bewertungsklassen und Interfaces implementier, Klassen für Strategy Pattern implementiert</t>
+  </si>
+  <si>
+    <t>Zu Hause                                                                               Klassen: CurriculumAlgo, IScheduleGenerator</t>
+  </si>
+  <si>
+    <t>Zu Hause                                                                               Klassen: CurriculumValuation, Datenmanager, IPersistenceService, IScheduleEvaluator, OffPeak_BetweenHours_EfficientRoomUsingValuation</t>
+  </si>
+  <si>
+    <t>Zu Hause                                                                               Klassen: MinimizeRoomChangeValuation, Program, EqualRoomUsingValuation, Combination, ClassNotMoreThenSixLessonsValutation</t>
+  </si>
+  <si>
+    <t>Use-Case Diagramm für die Tests</t>
+  </si>
+  <si>
+    <t>Arbeitsrapport Tag 7</t>
   </si>
 </sst>
 </file>
@@ -270,7 +315,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -327,6 +372,11 @@
       <b/>
       <sz val="60"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Archivo"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="-0.499984740745262"/>
       <name val="Archivo"/>
     </font>
   </fonts>
@@ -528,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -595,20 +645,33 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -629,9 +692,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -648,6 +708,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>22302</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>376521</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>2510118</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>1900520</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B06D716E-526F-E180-3D7C-099B532977F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11909502" y="26643109"/>
+          <a:ext cx="2487816" cy="1523999"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -851,8 +960,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L80"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.75" customHeight="1" zeroHeight="1"/>
+  <dimension ref="A1:L97"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
     <col min="1" max="2" width="6.88671875" customWidth="1"/>
     <col min="3" max="3" width="3.33203125" customWidth="1"/>
@@ -860,7 +969,8 @@
     <col min="5" max="5" width="37.44140625" customWidth="1"/>
     <col min="6" max="6" width="41.5546875" customWidth="1"/>
     <col min="7" max="7" width="3.44140625" customWidth="1"/>
-    <col min="8" max="10" width="26" customWidth="1"/>
+    <col min="8" max="9" width="26" customWidth="1"/>
+    <col min="10" max="10" width="37.6640625" style="27" customWidth="1"/>
     <col min="11" max="12" width="8.88671875" customWidth="1"/>
     <col min="13" max="16384" width="12.5546875" hidden="1"/>
   </cols>
@@ -875,7 +985,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
+      <c r="J1" s="24"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
@@ -889,7 +999,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="25" t="s">
         <v>19</v>
       </c>
       <c r="K2" s="2"/>
@@ -907,7 +1017,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+      <c r="J3" s="26"/>
       <c r="K3" s="4"/>
       <c r="L3" s="1"/>
     </row>
@@ -939,17 +1049,17 @@
     <row r="17" spans="1:12" ht="32.25" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="32"/>
+      <c r="D17" s="35"/>
       <c r="E17" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="32"/>
+      <c r="G17" s="35"/>
       <c r="H17" s="7" t="s">
         <v>7</v>
       </c>
@@ -965,17 +1075,17 @@
     <row r="18" spans="1:12" ht="32.25" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="33">
+      <c r="C18" s="36">
         <v>45953</v>
       </c>
-      <c r="D18" s="34"/>
+      <c r="D18" s="37"/>
       <c r="E18" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="35" t="s">
+      <c r="F18" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="36"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="8">
         <v>30</v>
       </c>
@@ -991,17 +1101,17 @@
     <row r="19" spans="1:12" ht="32.25" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="26">
+      <c r="C19" s="31">
         <v>45953</v>
       </c>
-      <c r="D19" s="27"/>
+      <c r="D19" s="32"/>
       <c r="E19" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="30" t="s">
+      <c r="F19" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="31"/>
+      <c r="G19" s="34"/>
       <c r="H19" s="10">
         <v>30</v>
       </c>
@@ -1015,17 +1125,17 @@
     <row r="20" spans="1:12" ht="32.25" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="26">
+      <c r="C20" s="31">
         <v>45953</v>
       </c>
-      <c r="D20" s="27"/>
+      <c r="D20" s="32"/>
       <c r="E20" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F20" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="31"/>
+      <c r="G20" s="34"/>
       <c r="H20" s="10">
         <v>150</v>
       </c>
@@ -1039,17 +1149,17 @@
     <row r="21" spans="1:12" ht="32.25" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="26">
+      <c r="C21" s="31">
         <v>45953</v>
       </c>
-      <c r="D21" s="27"/>
+      <c r="D21" s="32"/>
       <c r="E21" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="30" t="s">
+      <c r="F21" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="31"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="10">
         <v>15</v>
       </c>
@@ -1065,17 +1175,17 @@
     <row r="22" spans="1:12" ht="32.25" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="26">
+      <c r="C22" s="31">
         <v>45953</v>
       </c>
-      <c r="D22" s="27"/>
+      <c r="D22" s="32"/>
       <c r="E22" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="30" t="s">
+      <c r="F22" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="31"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="10">
         <v>120</v>
       </c>
@@ -1089,17 +1199,17 @@
     <row r="23" spans="1:12" ht="32.25" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="26">
+      <c r="C23" s="31">
         <v>45956</v>
       </c>
-      <c r="D23" s="27"/>
+      <c r="D23" s="32"/>
       <c r="E23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="30" t="s">
+      <c r="F23" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="G23" s="31"/>
+      <c r="G23" s="34"/>
       <c r="H23" s="10">
         <v>120</v>
       </c>
@@ -1115,17 +1225,17 @@
     <row r="24" spans="1:12" ht="32.25" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="26">
+      <c r="C24" s="31">
         <v>45959</v>
       </c>
-      <c r="D24" s="27"/>
+      <c r="D24" s="32"/>
       <c r="E24" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="30" t="s">
+      <c r="F24" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G24" s="31"/>
+      <c r="G24" s="34"/>
       <c r="H24" s="10">
         <v>90</v>
       </c>
@@ -1141,17 +1251,17 @@
     <row r="25" spans="1:12" ht="32.25" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="26">
+      <c r="C25" s="31">
         <v>45960</v>
       </c>
-      <c r="D25" s="29"/>
+      <c r="D25" s="32"/>
       <c r="E25" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="29"/>
+      <c r="G25" s="34"/>
       <c r="H25" s="10">
         <v>30</v>
       </c>
@@ -1167,17 +1277,17 @@
     <row r="26" spans="1:12" ht="32.25" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="26">
+      <c r="C26" s="31">
         <v>45960</v>
       </c>
-      <c r="D26" s="27"/>
+      <c r="D26" s="32"/>
       <c r="E26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="31"/>
+      <c r="G26" s="34"/>
       <c r="H26" s="10">
         <v>180</v>
       </c>
@@ -1191,17 +1301,17 @@
     <row r="27" spans="1:12" ht="76.8" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="26">
+      <c r="C27" s="31">
         <v>45960</v>
       </c>
-      <c r="D27" s="27"/>
+      <c r="D27" s="32"/>
       <c r="E27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="30" t="s">
+      <c r="F27" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="31"/>
+      <c r="G27" s="34"/>
       <c r="H27" s="10">
         <v>30</v>
       </c>
@@ -1217,10 +1327,10 @@
     <row r="28" spans="1:12" ht="34.200000000000003" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="28">
+      <c r="C28" s="31">
         <v>45960</v>
       </c>
-      <c r="D28" s="25"/>
+      <c r="D28" s="32"/>
       <c r="E28" s="12" t="s">
         <v>10</v>
       </c>
@@ -1241,17 +1351,17 @@
     <row r="29" spans="1:12" ht="72" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="26">
+      <c r="C29" s="31">
         <v>45960</v>
       </c>
-      <c r="D29" s="27"/>
+      <c r="D29" s="32"/>
       <c r="E29" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="30" t="s">
+      <c r="F29" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="G29" s="31"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="12">
         <v>30</v>
       </c>
@@ -1267,17 +1377,17 @@
     <row r="30" spans="1:12" ht="32.25" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="28">
+      <c r="C30" s="31">
         <v>45960</v>
       </c>
-      <c r="D30" s="25"/>
+      <c r="D30" s="32"/>
       <c r="E30" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F30" s="24" t="s">
+      <c r="F30" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G30" s="25"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="12">
         <v>10</v>
       </c>
@@ -1291,17 +1401,17 @@
     <row r="31" spans="1:12" ht="32.25" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="28">
+      <c r="C31" s="31">
         <v>45961</v>
       </c>
-      <c r="D31" s="25"/>
+      <c r="D31" s="32"/>
       <c r="E31" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="24" t="s">
+      <c r="F31" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="25"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="12">
         <v>30</v>
       </c>
@@ -1315,17 +1425,17 @@
     <row r="32" spans="1:12" ht="32.25" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="28">
+      <c r="C32" s="31">
         <v>45961</v>
       </c>
-      <c r="D32" s="25"/>
+      <c r="D32" s="32"/>
       <c r="E32" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F32" s="24" t="s">
+      <c r="F32" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="G32" s="25"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="12">
         <v>10</v>
       </c>
@@ -1339,17 +1449,17 @@
     <row r="33" spans="1:12" ht="32.25" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="28">
+      <c r="C33" s="31">
         <v>45965</v>
       </c>
-      <c r="D33" s="25"/>
+      <c r="D33" s="32"/>
       <c r="E33" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="G33" s="25"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="12">
         <v>150</v>
       </c>
@@ -1365,17 +1475,17 @@
     <row r="34" spans="1:12" ht="32.25" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="28">
+      <c r="C34" s="31">
         <v>45966</v>
       </c>
-      <c r="D34" s="25"/>
+      <c r="D34" s="32"/>
       <c r="E34" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="G34" s="25"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="12">
         <v>120</v>
       </c>
@@ -1391,17 +1501,17 @@
     <row r="35" spans="1:12" ht="32.25" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="28">
+      <c r="C35" s="31">
         <v>45967</v>
       </c>
-      <c r="D35" s="25"/>
+      <c r="D35" s="32"/>
       <c r="E35" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="24" t="s">
+      <c r="F35" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="25"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="12">
         <v>20</v>
       </c>
@@ -1417,17 +1527,17 @@
     <row r="36" spans="1:12" ht="32.25" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="28">
+      <c r="C36" s="31">
         <v>45967</v>
       </c>
-      <c r="D36" s="25"/>
+      <c r="D36" s="32"/>
       <c r="E36" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="G36" s="25"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="12">
         <v>30</v>
       </c>
@@ -1441,17 +1551,17 @@
     <row r="37" spans="1:12" ht="32.25" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="28">
+      <c r="C37" s="31">
         <v>45967</v>
       </c>
-      <c r="D37" s="25"/>
+      <c r="D37" s="32"/>
       <c r="E37" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="G37" s="25"/>
+      <c r="G37" s="34"/>
       <c r="H37" s="12">
         <v>60</v>
       </c>
@@ -1465,17 +1575,17 @@
     <row r="38" spans="1:12" ht="32.25" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="5"/>
-      <c r="C38" s="28">
+      <c r="C38" s="31">
         <v>45967</v>
       </c>
-      <c r="D38" s="25"/>
+      <c r="D38" s="32"/>
       <c r="E38" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="G38" s="25"/>
+      <c r="G38" s="34"/>
       <c r="H38" s="12">
         <v>30</v>
       </c>
@@ -1489,17 +1599,17 @@
     <row r="39" spans="1:12" ht="32.25" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="28">
+      <c r="C39" s="31">
         <v>45967</v>
       </c>
-      <c r="D39" s="25"/>
+      <c r="D39" s="32"/>
       <c r="E39" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="G39" s="25"/>
+      <c r="G39" s="34"/>
       <c r="H39" s="12">
         <v>30</v>
       </c>
@@ -1513,17 +1623,17 @@
     <row r="40" spans="1:12" ht="60" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="28">
+      <c r="C40" s="31">
         <v>45967</v>
       </c>
-      <c r="D40" s="25"/>
+      <c r="D40" s="32"/>
       <c r="E40" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F40" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="G40" s="25"/>
+      <c r="G40" s="34"/>
       <c r="H40" s="12">
         <v>30</v>
       </c>
@@ -1539,17 +1649,17 @@
     <row r="41" spans="1:12" ht="32.25" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="28">
+      <c r="C41" s="31">
         <v>45973</v>
       </c>
-      <c r="D41" s="25"/>
+      <c r="D41" s="32"/>
       <c r="E41" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="24" t="s">
+      <c r="F41" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="G41" s="25"/>
+      <c r="G41" s="34"/>
       <c r="H41" s="12">
         <v>120</v>
       </c>
@@ -1581,17 +1691,17 @@
     <row r="43" spans="1:12" ht="86.4" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="28">
+      <c r="C43" s="31">
         <v>45974</v>
       </c>
-      <c r="D43" s="25"/>
+      <c r="D43" s="32"/>
       <c r="E43" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="24" t="s">
+      <c r="F43" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="25"/>
+      <c r="G43" s="34"/>
       <c r="H43" s="12">
         <v>30</v>
       </c>
@@ -1607,17 +1717,17 @@
     <row r="44" spans="1:12" ht="32.25" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="28">
+      <c r="C44" s="31">
         <v>45974</v>
       </c>
-      <c r="D44" s="25"/>
+      <c r="D44" s="32"/>
       <c r="E44" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F44" s="24" t="s">
+      <c r="F44" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="G44" s="25"/>
+      <c r="G44" s="34"/>
       <c r="H44" s="12">
         <v>60</v>
       </c>
@@ -1631,17 +1741,17 @@
     <row r="45" spans="1:12" ht="32.25" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="26">
+      <c r="C45" s="31">
         <v>45974</v>
       </c>
-      <c r="D45" s="27"/>
+      <c r="D45" s="32"/>
       <c r="E45" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F45" s="24" t="s">
+      <c r="F45" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="G45" s="25"/>
+      <c r="G45" s="34"/>
       <c r="H45" s="12">
         <v>30</v>
       </c>
@@ -1657,17 +1767,17 @@
     <row r="46" spans="1:12" ht="50.4" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="26">
+      <c r="C46" s="31">
         <v>45974</v>
       </c>
-      <c r="D46" s="27"/>
+      <c r="D46" s="32"/>
       <c r="E46" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F46" s="24" t="s">
+      <c r="F46" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="G46" s="25"/>
+      <c r="G46" s="34"/>
       <c r="H46" s="12">
         <v>30</v>
       </c>
@@ -1683,17 +1793,17 @@
     <row r="47" spans="1:12" ht="32.25" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="26">
+      <c r="C47" s="31">
         <v>45974</v>
       </c>
-      <c r="D47" s="27"/>
+      <c r="D47" s="32"/>
       <c r="E47" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="24" t="s">
+      <c r="F47" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="G47" s="25"/>
+      <c r="G47" s="34"/>
       <c r="H47" s="12">
         <v>20</v>
       </c>
@@ -1709,17 +1819,17 @@
     <row r="48" spans="1:12" ht="32.25" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="26">
+      <c r="C48" s="31">
         <v>45980</v>
       </c>
-      <c r="D48" s="27"/>
+      <c r="D48" s="32"/>
       <c r="E48" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F48" s="24" t="s">
+      <c r="F48" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="G48" s="25"/>
+      <c r="G48" s="34"/>
       <c r="H48" s="12">
         <v>60</v>
       </c>
@@ -1735,17 +1845,17 @@
     <row r="49" spans="1:12" ht="32.25" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="26">
+      <c r="C49" s="31">
         <v>45980</v>
       </c>
-      <c r="D49" s="27"/>
+      <c r="D49" s="32"/>
       <c r="E49" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F49" s="24" t="s">
+      <c r="F49" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="G49" s="25"/>
+      <c r="G49" s="34"/>
       <c r="H49" s="12">
         <v>120</v>
       </c>
@@ -1761,17 +1871,17 @@
     <row r="50" spans="1:12" ht="32.25" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="26">
+      <c r="C50" s="31">
         <v>45981</v>
       </c>
-      <c r="D50" s="27"/>
+      <c r="D50" s="32"/>
       <c r="E50" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F50" s="24" t="s">
+      <c r="F50" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="G50" s="25"/>
+      <c r="G50" s="34"/>
       <c r="H50" s="12">
         <v>100</v>
       </c>
@@ -1785,17 +1895,17 @@
     <row r="51" spans="1:12" ht="32.25" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="26">
+      <c r="C51" s="31">
         <v>45981</v>
       </c>
-      <c r="D51" s="27"/>
+      <c r="D51" s="32"/>
       <c r="E51" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F51" s="24" t="s">
+      <c r="F51" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="G51" s="25"/>
+      <c r="G51" s="34"/>
       <c r="H51" s="12">
         <v>30</v>
       </c>
@@ -1809,17 +1919,17 @@
     <row r="52" spans="1:12" ht="59.4" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="5"/>
-      <c r="C52" s="26">
+      <c r="C52" s="31">
         <v>45981</v>
       </c>
-      <c r="D52" s="27"/>
+      <c r="D52" s="32"/>
       <c r="E52" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="24" t="s">
+      <c r="F52" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="G52" s="25"/>
+      <c r="G52" s="34"/>
       <c r="H52" s="12">
         <v>80</v>
       </c>
@@ -1835,17 +1945,17 @@
     <row r="53" spans="1:12" ht="32.25" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="5"/>
-      <c r="C53" s="26">
+      <c r="C53" s="31">
         <v>45981</v>
       </c>
-      <c r="D53" s="27"/>
+      <c r="D53" s="32"/>
       <c r="E53" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F53" s="24" t="s">
+      <c r="F53" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="G53" s="25"/>
+      <c r="G53" s="34"/>
       <c r="H53" s="12">
         <v>15</v>
       </c>
@@ -1859,17 +1969,17 @@
     <row r="54" spans="1:12" ht="32.25" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="5"/>
-      <c r="C54" s="26">
+      <c r="C54" s="31">
         <v>45981</v>
       </c>
-      <c r="D54" s="27"/>
+      <c r="D54" s="32"/>
       <c r="E54" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F54" s="24" t="s">
+      <c r="F54" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="G54" s="25"/>
+      <c r="G54" s="34"/>
       <c r="H54" s="12">
         <v>40</v>
       </c>
@@ -1883,17 +1993,17 @@
     <row r="55" spans="1:12" ht="32.25" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="5"/>
-      <c r="C55" s="26">
+      <c r="C55" s="31">
         <v>45986</v>
       </c>
-      <c r="D55" s="27"/>
+      <c r="D55" s="32"/>
       <c r="E55" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F55" s="24" t="s">
+      <c r="F55" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="G55" s="25"/>
+      <c r="G55" s="34"/>
       <c r="H55" s="12">
         <v>120</v>
       </c>
@@ -1909,17 +2019,17 @@
     <row r="56" spans="1:12" ht="50.4" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="5"/>
-      <c r="C56" s="26">
+      <c r="C56" s="31">
         <v>45987</v>
       </c>
-      <c r="D56" s="27"/>
+      <c r="D56" s="32"/>
       <c r="E56" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F56" s="24" t="s">
+      <c r="F56" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="G56" s="25"/>
+      <c r="G56" s="34"/>
       <c r="H56" s="12">
         <v>240</v>
       </c>
@@ -1935,17 +2045,17 @@
     <row r="57" spans="1:12" ht="32.25" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="5"/>
-      <c r="C57" s="26">
+      <c r="C57" s="31">
         <v>45988</v>
       </c>
-      <c r="D57" s="27"/>
+      <c r="D57" s="32"/>
       <c r="E57" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F57" s="24" t="s">
+      <c r="F57" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="G57" s="25"/>
+      <c r="G57" s="34"/>
       <c r="H57" s="12">
         <v>15</v>
       </c>
@@ -1959,17 +2069,17 @@
     <row r="58" spans="1:12" ht="32.25" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="5"/>
-      <c r="C58" s="26">
+      <c r="C58" s="31">
         <v>45988</v>
       </c>
-      <c r="D58" s="27"/>
+      <c r="D58" s="32"/>
       <c r="E58" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F58" s="24" t="s">
+      <c r="F58" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="G58" s="25"/>
+      <c r="G58" s="34"/>
       <c r="H58" s="12">
         <v>15</v>
       </c>
@@ -1983,17 +2093,17 @@
     <row r="59" spans="1:12" ht="32.25" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="5"/>
-      <c r="C59" s="26">
+      <c r="C59" s="31">
         <v>45988</v>
       </c>
-      <c r="D59" s="27"/>
+      <c r="D59" s="32"/>
       <c r="E59" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="24" t="s">
+      <c r="F59" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="G59" s="25"/>
+      <c r="G59" s="34"/>
       <c r="H59" s="12">
         <v>40</v>
       </c>
@@ -2007,17 +2117,17 @@
     <row r="60" spans="1:12" ht="32.25" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="5"/>
-      <c r="C60" s="26">
+      <c r="C60" s="31">
         <v>45988</v>
       </c>
-      <c r="D60" s="27"/>
+      <c r="D60" s="32"/>
       <c r="E60" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F60" s="24" t="s">
+      <c r="F60" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="G60" s="25"/>
+      <c r="G60" s="34"/>
       <c r="H60" s="12">
         <v>30</v>
       </c>
@@ -2028,20 +2138,20 @@
       <c r="K60" s="6"/>
       <c r="L60" s="1"/>
     </row>
-    <row r="61" spans="1:12" ht="32.25" customHeight="1">
+    <row r="61" spans="1:12" ht="67.2" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="5"/>
-      <c r="C61" s="26">
+      <c r="C61" s="31">
         <v>45988</v>
       </c>
-      <c r="D61" s="27"/>
+      <c r="D61" s="32"/>
       <c r="E61" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F61" s="24" t="s">
+      <c r="F61" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="G61" s="25"/>
+      <c r="G61" s="34"/>
       <c r="H61" s="12">
         <v>120</v>
       </c>
@@ -2054,20 +2164,20 @@
       <c r="K61" s="6"/>
       <c r="L61" s="1"/>
     </row>
-    <row r="62" spans="1:12" ht="32.25" customHeight="1">
+    <row r="62" spans="1:12" ht="31.8" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="5"/>
-      <c r="C62" s="26">
+      <c r="C62" s="31">
         <v>45988</v>
       </c>
-      <c r="D62" s="27"/>
+      <c r="D62" s="32"/>
       <c r="E62" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F62" s="24" t="s">
+      <c r="F62" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="G62" s="25"/>
+      <c r="G62" s="34"/>
       <c r="H62" s="12">
         <v>120</v>
       </c>
@@ -2078,20 +2188,20 @@
       <c r="K62" s="6"/>
       <c r="L62" s="1"/>
     </row>
-    <row r="63" spans="1:12" ht="32.25" customHeight="1">
+    <row r="63" spans="1:12" ht="31.8" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="5"/>
-      <c r="C63" s="26">
+      <c r="C63" s="31">
         <v>45988</v>
       </c>
-      <c r="D63" s="27"/>
+      <c r="D63" s="32"/>
       <c r="E63" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F63" s="24" t="s">
+      <c r="F63" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="G63" s="25"/>
+      <c r="G63" s="34"/>
       <c r="H63" s="12">
         <v>10</v>
       </c>
@@ -2102,20 +2212,20 @@
       <c r="K63" s="6"/>
       <c r="L63" s="1"/>
     </row>
-    <row r="64" spans="1:12" ht="32.25" customHeight="1">
+    <row r="64" spans="1:12" ht="31.8" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="5"/>
-      <c r="C64" s="26">
+      <c r="C64" s="31">
         <v>45988</v>
       </c>
-      <c r="D64" s="27"/>
+      <c r="D64" s="32"/>
       <c r="E64" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F64" s="24" t="s">
+      <c r="F64" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="G64" s="25"/>
+      <c r="G64" s="34"/>
       <c r="H64" s="12">
         <v>20</v>
       </c>
@@ -2126,20 +2236,20 @@
       <c r="K64" s="6"/>
       <c r="L64" s="1"/>
     </row>
-    <row r="65" spans="1:12" ht="32.25" customHeight="1">
+    <row r="65" spans="1:12" ht="31.8" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="5"/>
-      <c r="C65" s="26">
+      <c r="C65" s="31">
         <v>45988</v>
       </c>
-      <c r="D65" s="27"/>
+      <c r="D65" s="32"/>
       <c r="E65" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="24" t="s">
+      <c r="F65" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="G65" s="25"/>
+      <c r="G65" s="34"/>
       <c r="H65" s="12">
         <v>30</v>
       </c>
@@ -2150,13 +2260,13 @@
       <c r="K65" s="6"/>
       <c r="L65" s="1"/>
     </row>
-    <row r="66" spans="1:12" ht="32.25" customHeight="1">
+    <row r="66" spans="1:12" ht="184.8" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="5"/>
-      <c r="C66" s="26">
+      <c r="C66" s="31">
         <v>45988</v>
       </c>
-      <c r="D66" s="27"/>
+      <c r="D66" s="32"/>
       <c r="E66" s="12" t="s">
         <v>11</v>
       </c>
@@ -2165,94 +2275,468 @@
       </c>
       <c r="G66" s="22"/>
       <c r="H66" s="12">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="I66" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="13"/>
+      <c r="J66" s="29"/>
       <c r="K66" s="6"/>
       <c r="L66" s="1"/>
     </row>
-    <row r="67" spans="1:12" ht="32.25" customHeight="1">
+    <row r="67" spans="1:12" ht="62.4" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="5"/>
-      <c r="C67" s="26">
+      <c r="C67" s="31">
         <v>45988</v>
       </c>
-      <c r="D67" s="27"/>
+      <c r="D67" s="32"/>
       <c r="E67" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="G67" s="25"/>
-      <c r="H67" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="G67" s="34"/>
+      <c r="H67" s="12">
+        <v>150</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="13"/>
+      <c r="J67" s="13" t="s">
+        <v>78</v>
+      </c>
       <c r="K67" s="6"/>
       <c r="L67" s="1"/>
     </row>
-    <row r="68" spans="1:12" ht="24.75" customHeight="1">
+    <row r="68" spans="1:12" ht="31.8" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
-      <c r="K68" s="16"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="31">
+        <v>45988</v>
+      </c>
+      <c r="D68" s="32"/>
+      <c r="E68" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="G68" s="34"/>
+      <c r="H68" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I68" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J68" s="13"/>
+      <c r="K68" s="6"/>
       <c r="L68" s="1"/>
     </row>
-    <row r="69" spans="1:12" ht="24.75" customHeight="1">
+    <row r="69" spans="1:12" ht="31.8" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="31">
+        <v>45995</v>
+      </c>
+      <c r="D69" s="32"/>
+      <c r="E69" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="G69" s="34"/>
+      <c r="H69" s="12">
+        <v>30</v>
+      </c>
+      <c r="I69" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J69" s="13"/>
+      <c r="K69" s="6"/>
       <c r="L69" s="1"/>
     </row>
-    <row r="70" spans="1:12" ht="24.75" customHeight="1">
-      <c r="A70" s="37"/>
-      <c r="B70" s="37"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="17"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
+    <row r="70" spans="1:12" ht="31.8" customHeight="1">
+      <c r="A70" s="1"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="31">
+        <v>45995</v>
+      </c>
+      <c r="D70" s="32"/>
+      <c r="E70" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F70" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="G70" s="34"/>
+      <c r="H70" s="12">
+        <v>100</v>
+      </c>
+      <c r="I70" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J70" s="13"/>
+      <c r="K70" s="6"/>
       <c r="L70" s="1"/>
     </row>
-    <row r="71" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="72" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="73" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="74" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="75" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="76" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="77" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="78" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="79" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="80" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="71" spans="1:12" ht="31.8" customHeight="1">
+      <c r="A71" s="1"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="31">
+        <v>45997</v>
+      </c>
+      <c r="D71" s="32"/>
+      <c r="E71" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="G71" s="34"/>
+      <c r="H71" s="12">
+        <v>180</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J71" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K71" s="6"/>
+      <c r="L71" s="1"/>
+    </row>
+    <row r="72" spans="1:12" ht="94.8" customHeight="1">
+      <c r="A72" s="1"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="31">
+        <v>45999</v>
+      </c>
+      <c r="D72" s="32"/>
+      <c r="E72" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G72" s="34"/>
+      <c r="H72" s="12">
+        <v>180</v>
+      </c>
+      <c r="I72" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="K72" s="6"/>
+      <c r="L72" s="1"/>
+    </row>
+    <row r="73" spans="1:12" ht="69" customHeight="1">
+      <c r="A73" s="1"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="31">
+        <v>46000</v>
+      </c>
+      <c r="D73" s="32"/>
+      <c r="E73" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G73" s="34"/>
+      <c r="H73" s="12">
+        <v>180</v>
+      </c>
+      <c r="I73" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J73" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="K73" s="6"/>
+      <c r="L73" s="1"/>
+    </row>
+    <row r="74" spans="1:12" ht="103.2" customHeight="1">
+      <c r="A74" s="1"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="31">
+        <v>46001</v>
+      </c>
+      <c r="D74" s="32"/>
+      <c r="E74" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F74" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G74" s="34"/>
+      <c r="H74" s="12">
+        <v>180</v>
+      </c>
+      <c r="I74" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J74" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="K74" s="6"/>
+      <c r="L74" s="1"/>
+    </row>
+    <row r="75" spans="1:12" ht="31.8" customHeight="1">
+      <c r="A75" s="1"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="31">
+        <v>46002</v>
+      </c>
+      <c r="D75" s="32"/>
+      <c r="E75" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G75" s="34"/>
+      <c r="H75" s="12">
+        <v>30</v>
+      </c>
+      <c r="I75" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J75" s="13"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="1"/>
+    </row>
+    <row r="76" spans="1:12" ht="31.8" customHeight="1">
+      <c r="A76" s="1"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="31">
+        <v>46002</v>
+      </c>
+      <c r="D76" s="32"/>
+      <c r="E76" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="G76" s="34"/>
+      <c r="H76" s="12">
+        <v>40</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J76" s="13"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="1"/>
+    </row>
+    <row r="77" spans="1:12" ht="31.8" customHeight="1">
+      <c r="A77" s="1"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="31"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="33"/>
+      <c r="G77" s="34"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="1"/>
+    </row>
+    <row r="78" spans="1:12" ht="31.8" customHeight="1">
+      <c r="A78" s="1"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="31"/>
+      <c r="D78" s="32"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="33"/>
+      <c r="G78" s="34"/>
+      <c r="H78" s="12"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="1"/>
+    </row>
+    <row r="79" spans="1:12" ht="31.8" customHeight="1">
+      <c r="A79" s="1"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="31"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="33"/>
+      <c r="G79" s="34"/>
+      <c r="H79" s="12"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="13"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="1"/>
+    </row>
+    <row r="80" spans="1:12" ht="24.75" customHeight="1">
+      <c r="A80" s="1"/>
+      <c r="B80" s="14"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="15"/>
+      <c r="H80" s="15"/>
+      <c r="I80" s="15"/>
+      <c r="J80" s="28"/>
+      <c r="K80" s="16"/>
+      <c r="L80" s="1"/>
+    </row>
+    <row r="81" spans="1:12" ht="24.75" customHeight="1">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="24"/>
+      <c r="K81" s="1"/>
+      <c r="L81" s="1"/>
+    </row>
+    <row r="82" spans="1:12" ht="24.75" customHeight="1">
+      <c r="A82" s="30"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="30"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
+      <c r="F82" s="17"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="24"/>
+      <c r="K82" s="1"/>
+      <c r="L82" s="1"/>
+    </row>
+    <row r="83" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="84" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="85" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="86" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="87" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="88" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="89" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="90" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="91" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="92" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="93" spans="1:12" ht="0" hidden="1" customHeight="1"/>
+    <row r="94" spans="1:12" ht="0" hidden="1" customHeight="1"/>
+    <row r="95" spans="1:12" ht="0" hidden="1" customHeight="1"/>
+    <row r="96" spans="1:12" ht="0" hidden="1" customHeight="1"/>
+    <row r="97" ht="0" hidden="1" customHeight="1"/>
   </sheetData>
-  <mergeCells count="99">
-    <mergeCell ref="A70:E70"/>
+  <mergeCells count="123">
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="A82:E82"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C29:D29"/>
@@ -2268,91 +2752,15 @@
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="F35:G35"/>
     <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C70:D70"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="F39:G39"/>
     <mergeCell ref="F40:G40"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C59:D59"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/docs/Arbeitsrapport.xlsx
+++ b/docs/Arbeitsrapport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brtoz\Codes\IPT5.1\Stundenplaner-Projekt\IPT5.1_Stundenplaner-Projekt\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08AD5BB-442D-4663-A76B-39792E97A105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58F376B-157A-4AA7-B131-897BDE9FD602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2676" yWindow="2508" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Sales Report Form" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
   <si>
     <t>Datum</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>Arbeitsrapport Tag 7</t>
+  </si>
+  <si>
+    <t>UnitTest Beschreibung</t>
   </si>
 </sst>
 </file>
@@ -663,35 +666,35 @@
     <xf numFmtId="164" fontId="10" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -960,7 +963,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
     <col min="1" max="2" width="6.88671875" customWidth="1"/>
@@ -1049,17 +1052,17 @@
     <row r="17" spans="1:12" ht="32.25" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="35"/>
+      <c r="D17" s="34"/>
       <c r="E17" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F17" s="35" t="s">
+      <c r="F17" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="35"/>
+      <c r="G17" s="34"/>
       <c r="H17" s="7" t="s">
         <v>7</v>
       </c>
@@ -1075,17 +1078,17 @@
     <row r="18" spans="1:12" ht="32.25" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="36">
+      <c r="C18" s="35">
         <v>45953</v>
       </c>
-      <c r="D18" s="37"/>
+      <c r="D18" s="36"/>
       <c r="E18" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="38" t="s">
+      <c r="F18" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="39"/>
+      <c r="G18" s="38"/>
       <c r="H18" s="8">
         <v>30</v>
       </c>
@@ -1101,17 +1104,17 @@
     <row r="19" spans="1:12" ht="32.25" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="31">
+      <c r="C19" s="30">
         <v>45953</v>
       </c>
-      <c r="D19" s="32"/>
+      <c r="D19" s="31"/>
       <c r="E19" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="F19" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="34"/>
+      <c r="G19" s="33"/>
       <c r="H19" s="10">
         <v>30</v>
       </c>
@@ -1125,17 +1128,17 @@
     <row r="20" spans="1:12" ht="32.25" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="31">
+      <c r="C20" s="30">
         <v>45953</v>
       </c>
-      <c r="D20" s="32"/>
+      <c r="D20" s="31"/>
       <c r="E20" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="F20" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="34"/>
+      <c r="G20" s="33"/>
       <c r="H20" s="10">
         <v>150</v>
       </c>
@@ -1149,17 +1152,17 @@
     <row r="21" spans="1:12" ht="32.25" customHeight="1">
       <c r="A21" s="1"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="31">
+      <c r="C21" s="30">
         <v>45953</v>
       </c>
-      <c r="D21" s="32"/>
+      <c r="D21" s="31"/>
       <c r="E21" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F21" s="33" t="s">
+      <c r="F21" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="34"/>
+      <c r="G21" s="33"/>
       <c r="H21" s="10">
         <v>15</v>
       </c>
@@ -1175,17 +1178,17 @@
     <row r="22" spans="1:12" ht="32.25" customHeight="1">
       <c r="A22" s="1"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="31">
+      <c r="C22" s="30">
         <v>45953</v>
       </c>
-      <c r="D22" s="32"/>
+      <c r="D22" s="31"/>
       <c r="E22" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="33" t="s">
+      <c r="F22" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="34"/>
+      <c r="G22" s="33"/>
       <c r="H22" s="10">
         <v>120</v>
       </c>
@@ -1199,17 +1202,17 @@
     <row r="23" spans="1:12" ht="32.25" customHeight="1">
       <c r="A23" s="1"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="31">
+      <c r="C23" s="30">
         <v>45956</v>
       </c>
-      <c r="D23" s="32"/>
+      <c r="D23" s="31"/>
       <c r="E23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="33" t="s">
+      <c r="F23" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="G23" s="34"/>
+      <c r="G23" s="33"/>
       <c r="H23" s="10">
         <v>120</v>
       </c>
@@ -1225,17 +1228,17 @@
     <row r="24" spans="1:12" ht="32.25" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="31">
+      <c r="C24" s="30">
         <v>45959</v>
       </c>
-      <c r="D24" s="32"/>
+      <c r="D24" s="31"/>
       <c r="E24" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="33" t="s">
+      <c r="F24" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="G24" s="34"/>
+      <c r="G24" s="33"/>
       <c r="H24" s="10">
         <v>90</v>
       </c>
@@ -1251,17 +1254,17 @@
     <row r="25" spans="1:12" ht="32.25" customHeight="1">
       <c r="A25" s="1"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="31">
+      <c r="C25" s="30">
         <v>45960</v>
       </c>
-      <c r="D25" s="32"/>
+      <c r="D25" s="31"/>
       <c r="E25" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="G25" s="34"/>
+      <c r="G25" s="33"/>
       <c r="H25" s="10">
         <v>30</v>
       </c>
@@ -1277,17 +1280,17 @@
     <row r="26" spans="1:12" ht="32.25" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="31">
+      <c r="C26" s="30">
         <v>45960</v>
       </c>
-      <c r="D26" s="32"/>
+      <c r="D26" s="31"/>
       <c r="E26" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="34"/>
+      <c r="G26" s="33"/>
       <c r="H26" s="10">
         <v>180</v>
       </c>
@@ -1301,17 +1304,17 @@
     <row r="27" spans="1:12" ht="76.8" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="31">
+      <c r="C27" s="30">
         <v>45960</v>
       </c>
-      <c r="D27" s="32"/>
+      <c r="D27" s="31"/>
       <c r="E27" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="33" t="s">
+      <c r="F27" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="34"/>
+      <c r="G27" s="33"/>
       <c r="H27" s="10">
         <v>30</v>
       </c>
@@ -1327,10 +1330,10 @@
     <row r="28" spans="1:12" ht="34.200000000000003" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="31">
+      <c r="C28" s="30">
         <v>45960</v>
       </c>
-      <c r="D28" s="32"/>
+      <c r="D28" s="31"/>
       <c r="E28" s="12" t="s">
         <v>10</v>
       </c>
@@ -1351,17 +1354,17 @@
     <row r="29" spans="1:12" ht="72" customHeight="1">
       <c r="A29" s="1"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="31">
+      <c r="C29" s="30">
         <v>45960</v>
       </c>
-      <c r="D29" s="32"/>
+      <c r="D29" s="31"/>
       <c r="E29" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="F29" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="12">
         <v>30</v>
       </c>
@@ -1377,17 +1380,17 @@
     <row r="30" spans="1:12" ht="32.25" customHeight="1">
       <c r="A30" s="1"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="31">
+      <c r="C30" s="30">
         <v>45960</v>
       </c>
-      <c r="D30" s="32"/>
+      <c r="D30" s="31"/>
       <c r="E30" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F30" s="33" t="s">
+      <c r="F30" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="12">
         <v>10</v>
       </c>
@@ -1401,17 +1404,17 @@
     <row r="31" spans="1:12" ht="32.25" customHeight="1">
       <c r="A31" s="1"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="31">
+      <c r="C31" s="30">
         <v>45961</v>
       </c>
-      <c r="D31" s="32"/>
+      <c r="D31" s="31"/>
       <c r="E31" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F31" s="33" t="s">
+      <c r="F31" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="12">
         <v>30</v>
       </c>
@@ -1425,17 +1428,17 @@
     <row r="32" spans="1:12" ht="32.25" customHeight="1">
       <c r="A32" s="1"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="31">
+      <c r="C32" s="30">
         <v>45961</v>
       </c>
-      <c r="D32" s="32"/>
+      <c r="D32" s="31"/>
       <c r="E32" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F32" s="33" t="s">
+      <c r="F32" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="12">
         <v>10</v>
       </c>
@@ -1449,17 +1452,17 @@
     <row r="33" spans="1:12" ht="32.25" customHeight="1">
       <c r="A33" s="1"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="31">
+      <c r="C33" s="30">
         <v>45965</v>
       </c>
-      <c r="D33" s="32"/>
+      <c r="D33" s="31"/>
       <c r="E33" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="33" t="s">
+      <c r="F33" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="12">
         <v>150</v>
       </c>
@@ -1475,17 +1478,17 @@
     <row r="34" spans="1:12" ht="32.25" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="31">
+      <c r="C34" s="30">
         <v>45966</v>
       </c>
-      <c r="D34" s="32"/>
+      <c r="D34" s="31"/>
       <c r="E34" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="33" t="s">
+      <c r="F34" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="12">
         <v>120</v>
       </c>
@@ -1501,17 +1504,17 @@
     <row r="35" spans="1:12" ht="32.25" customHeight="1">
       <c r="A35" s="1"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="31">
+      <c r="C35" s="30">
         <v>45967</v>
       </c>
-      <c r="D35" s="32"/>
+      <c r="D35" s="31"/>
       <c r="E35" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="33" t="s">
+      <c r="F35" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="33"/>
       <c r="H35" s="12">
         <v>20</v>
       </c>
@@ -1527,17 +1530,17 @@
     <row r="36" spans="1:12" ht="32.25" customHeight="1">
       <c r="A36" s="1"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="31">
+      <c r="C36" s="30">
         <v>45967</v>
       </c>
-      <c r="D36" s="32"/>
+      <c r="D36" s="31"/>
       <c r="E36" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="33" t="s">
+      <c r="F36" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="12">
         <v>30</v>
       </c>
@@ -1551,17 +1554,17 @@
     <row r="37" spans="1:12" ht="32.25" customHeight="1">
       <c r="A37" s="1"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="31">
+      <c r="C37" s="30">
         <v>45967</v>
       </c>
-      <c r="D37" s="32"/>
+      <c r="D37" s="31"/>
       <c r="E37" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="33" t="s">
+      <c r="F37" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="G37" s="34"/>
+      <c r="G37" s="33"/>
       <c r="H37" s="12">
         <v>60</v>
       </c>
@@ -1575,17 +1578,17 @@
     <row r="38" spans="1:12" ht="32.25" customHeight="1">
       <c r="A38" s="1"/>
       <c r="B38" s="5"/>
-      <c r="C38" s="31">
+      <c r="C38" s="30">
         <v>45967</v>
       </c>
-      <c r="D38" s="32"/>
+      <c r="D38" s="31"/>
       <c r="E38" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="33" t="s">
+      <c r="F38" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G38" s="34"/>
+      <c r="G38" s="33"/>
       <c r="H38" s="12">
         <v>30</v>
       </c>
@@ -1599,17 +1602,17 @@
     <row r="39" spans="1:12" ht="32.25" customHeight="1">
       <c r="A39" s="1"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="31">
+      <c r="C39" s="30">
         <v>45967</v>
       </c>
-      <c r="D39" s="32"/>
+      <c r="D39" s="31"/>
       <c r="E39" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F39" s="33" t="s">
+      <c r="F39" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="G39" s="34"/>
+      <c r="G39" s="33"/>
       <c r="H39" s="12">
         <v>30</v>
       </c>
@@ -1623,17 +1626,17 @@
     <row r="40" spans="1:12" ht="60" customHeight="1">
       <c r="A40" s="1"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="31">
+      <c r="C40" s="30">
         <v>45967</v>
       </c>
-      <c r="D40" s="32"/>
+      <c r="D40" s="31"/>
       <c r="E40" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F40" s="33" t="s">
+      <c r="F40" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="G40" s="34"/>
+      <c r="G40" s="33"/>
       <c r="H40" s="12">
         <v>30</v>
       </c>
@@ -1649,17 +1652,17 @@
     <row r="41" spans="1:12" ht="32.25" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="31">
+      <c r="C41" s="30">
         <v>45973</v>
       </c>
-      <c r="D41" s="32"/>
+      <c r="D41" s="31"/>
       <c r="E41" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="G41" s="34"/>
+      <c r="G41" s="33"/>
       <c r="H41" s="12">
         <v>120</v>
       </c>
@@ -1691,17 +1694,17 @@
     <row r="43" spans="1:12" ht="86.4" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="31">
+      <c r="C43" s="30">
         <v>45974</v>
       </c>
-      <c r="D43" s="32"/>
+      <c r="D43" s="31"/>
       <c r="E43" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="33" t="s">
+      <c r="F43" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="G43" s="34"/>
+      <c r="G43" s="33"/>
       <c r="H43" s="12">
         <v>30</v>
       </c>
@@ -1717,17 +1720,17 @@
     <row r="44" spans="1:12" ht="32.25" customHeight="1">
       <c r="A44" s="1"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="31">
+      <c r="C44" s="30">
         <v>45974</v>
       </c>
-      <c r="D44" s="32"/>
+      <c r="D44" s="31"/>
       <c r="E44" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F44" s="33" t="s">
+      <c r="F44" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="G44" s="34"/>
+      <c r="G44" s="33"/>
       <c r="H44" s="12">
         <v>60</v>
       </c>
@@ -1741,17 +1744,17 @@
     <row r="45" spans="1:12" ht="32.25" customHeight="1">
       <c r="A45" s="1"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="31">
+      <c r="C45" s="30">
         <v>45974</v>
       </c>
-      <c r="D45" s="32"/>
+      <c r="D45" s="31"/>
       <c r="E45" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F45" s="33" t="s">
+      <c r="F45" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="G45" s="34"/>
+      <c r="G45" s="33"/>
       <c r="H45" s="12">
         <v>30</v>
       </c>
@@ -1767,17 +1770,17 @@
     <row r="46" spans="1:12" ht="50.4" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="31">
+      <c r="C46" s="30">
         <v>45974</v>
       </c>
-      <c r="D46" s="32"/>
+      <c r="D46" s="31"/>
       <c r="E46" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F46" s="33" t="s">
+      <c r="F46" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="G46" s="34"/>
+      <c r="G46" s="33"/>
       <c r="H46" s="12">
         <v>30</v>
       </c>
@@ -1793,17 +1796,17 @@
     <row r="47" spans="1:12" ht="32.25" customHeight="1">
       <c r="A47" s="1"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="31">
+      <c r="C47" s="30">
         <v>45974</v>
       </c>
-      <c r="D47" s="32"/>
+      <c r="D47" s="31"/>
       <c r="E47" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F47" s="33" t="s">
+      <c r="F47" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="G47" s="34"/>
+      <c r="G47" s="33"/>
       <c r="H47" s="12">
         <v>20</v>
       </c>
@@ -1819,17 +1822,17 @@
     <row r="48" spans="1:12" ht="32.25" customHeight="1">
       <c r="A48" s="1"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="31">
+      <c r="C48" s="30">
         <v>45980</v>
       </c>
-      <c r="D48" s="32"/>
+      <c r="D48" s="31"/>
       <c r="E48" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F48" s="33" t="s">
+      <c r="F48" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="G48" s="34"/>
+      <c r="G48" s="33"/>
       <c r="H48" s="12">
         <v>60</v>
       </c>
@@ -1845,17 +1848,17 @@
     <row r="49" spans="1:12" ht="32.25" customHeight="1">
       <c r="A49" s="1"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="31">
+      <c r="C49" s="30">
         <v>45980</v>
       </c>
-      <c r="D49" s="32"/>
+      <c r="D49" s="31"/>
       <c r="E49" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F49" s="33" t="s">
+      <c r="F49" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="G49" s="34"/>
+      <c r="G49" s="33"/>
       <c r="H49" s="12">
         <v>120</v>
       </c>
@@ -1871,17 +1874,17 @@
     <row r="50" spans="1:12" ht="32.25" customHeight="1">
       <c r="A50" s="1"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="31">
+      <c r="C50" s="30">
         <v>45981</v>
       </c>
-      <c r="D50" s="32"/>
+      <c r="D50" s="31"/>
       <c r="E50" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F50" s="33" t="s">
+      <c r="F50" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="G50" s="34"/>
+      <c r="G50" s="33"/>
       <c r="H50" s="12">
         <v>100</v>
       </c>
@@ -1895,17 +1898,17 @@
     <row r="51" spans="1:12" ht="32.25" customHeight="1">
       <c r="A51" s="1"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="31">
+      <c r="C51" s="30">
         <v>45981</v>
       </c>
-      <c r="D51" s="32"/>
+      <c r="D51" s="31"/>
       <c r="E51" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F51" s="33" t="s">
+      <c r="F51" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="G51" s="34"/>
+      <c r="G51" s="33"/>
       <c r="H51" s="12">
         <v>30</v>
       </c>
@@ -1919,17 +1922,17 @@
     <row r="52" spans="1:12" ht="59.4" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="5"/>
-      <c r="C52" s="31">
+      <c r="C52" s="30">
         <v>45981</v>
       </c>
-      <c r="D52" s="32"/>
+      <c r="D52" s="31"/>
       <c r="E52" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="33" t="s">
+      <c r="F52" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="G52" s="34"/>
+      <c r="G52" s="33"/>
       <c r="H52" s="12">
         <v>80</v>
       </c>
@@ -1945,17 +1948,17 @@
     <row r="53" spans="1:12" ht="32.25" customHeight="1">
       <c r="A53" s="1"/>
       <c r="B53" s="5"/>
-      <c r="C53" s="31">
+      <c r="C53" s="30">
         <v>45981</v>
       </c>
-      <c r="D53" s="32"/>
+      <c r="D53" s="31"/>
       <c r="E53" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F53" s="33" t="s">
+      <c r="F53" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="G53" s="34"/>
+      <c r="G53" s="33"/>
       <c r="H53" s="12">
         <v>15</v>
       </c>
@@ -1969,17 +1972,17 @@
     <row r="54" spans="1:12" ht="32.25" customHeight="1">
       <c r="A54" s="1"/>
       <c r="B54" s="5"/>
-      <c r="C54" s="31">
+      <c r="C54" s="30">
         <v>45981</v>
       </c>
-      <c r="D54" s="32"/>
+      <c r="D54" s="31"/>
       <c r="E54" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F54" s="33" t="s">
+      <c r="F54" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="G54" s="34"/>
+      <c r="G54" s="33"/>
       <c r="H54" s="12">
         <v>40</v>
       </c>
@@ -1993,17 +1996,17 @@
     <row r="55" spans="1:12" ht="32.25" customHeight="1">
       <c r="A55" s="1"/>
       <c r="B55" s="5"/>
-      <c r="C55" s="31">
+      <c r="C55" s="30">
         <v>45986</v>
       </c>
-      <c r="D55" s="32"/>
+      <c r="D55" s="31"/>
       <c r="E55" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F55" s="33" t="s">
+      <c r="F55" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="G55" s="34"/>
+      <c r="G55" s="33"/>
       <c r="H55" s="12">
         <v>120</v>
       </c>
@@ -2019,17 +2022,17 @@
     <row r="56" spans="1:12" ht="50.4" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="5"/>
-      <c r="C56" s="31">
+      <c r="C56" s="30">
         <v>45987</v>
       </c>
-      <c r="D56" s="32"/>
+      <c r="D56" s="31"/>
       <c r="E56" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F56" s="33" t="s">
+      <c r="F56" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="G56" s="34"/>
+      <c r="G56" s="33"/>
       <c r="H56" s="12">
         <v>240</v>
       </c>
@@ -2045,17 +2048,17 @@
     <row r="57" spans="1:12" ht="32.25" customHeight="1">
       <c r="A57" s="1"/>
       <c r="B57" s="5"/>
-      <c r="C57" s="31">
+      <c r="C57" s="30">
         <v>45988</v>
       </c>
-      <c r="D57" s="32"/>
+      <c r="D57" s="31"/>
       <c r="E57" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F57" s="33" t="s">
+      <c r="F57" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="G57" s="34"/>
+      <c r="G57" s="33"/>
       <c r="H57" s="12">
         <v>15</v>
       </c>
@@ -2069,17 +2072,17 @@
     <row r="58" spans="1:12" ht="32.25" customHeight="1">
       <c r="A58" s="1"/>
       <c r="B58" s="5"/>
-      <c r="C58" s="31">
+      <c r="C58" s="30">
         <v>45988</v>
       </c>
-      <c r="D58" s="32"/>
+      <c r="D58" s="31"/>
       <c r="E58" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F58" s="33" t="s">
+      <c r="F58" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="G58" s="34"/>
+      <c r="G58" s="33"/>
       <c r="H58" s="12">
         <v>15</v>
       </c>
@@ -2093,17 +2096,17 @@
     <row r="59" spans="1:12" ht="32.25" customHeight="1">
       <c r="A59" s="1"/>
       <c r="B59" s="5"/>
-      <c r="C59" s="31">
+      <c r="C59" s="30">
         <v>45988</v>
       </c>
-      <c r="D59" s="32"/>
+      <c r="D59" s="31"/>
       <c r="E59" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F59" s="33" t="s">
+      <c r="F59" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="G59" s="34"/>
+      <c r="G59" s="33"/>
       <c r="H59" s="12">
         <v>40</v>
       </c>
@@ -2117,17 +2120,17 @@
     <row r="60" spans="1:12" ht="32.25" customHeight="1">
       <c r="A60" s="1"/>
       <c r="B60" s="5"/>
-      <c r="C60" s="31">
+      <c r="C60" s="30">
         <v>45988</v>
       </c>
-      <c r="D60" s="32"/>
+      <c r="D60" s="31"/>
       <c r="E60" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F60" s="33" t="s">
+      <c r="F60" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="G60" s="34"/>
+      <c r="G60" s="33"/>
       <c r="H60" s="12">
         <v>30</v>
       </c>
@@ -2141,17 +2144,17 @@
     <row r="61" spans="1:12" ht="67.2" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="5"/>
-      <c r="C61" s="31">
+      <c r="C61" s="30">
         <v>45988</v>
       </c>
-      <c r="D61" s="32"/>
+      <c r="D61" s="31"/>
       <c r="E61" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F61" s="33" t="s">
+      <c r="F61" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="G61" s="34"/>
+      <c r="G61" s="33"/>
       <c r="H61" s="12">
         <v>120</v>
       </c>
@@ -2167,17 +2170,17 @@
     <row r="62" spans="1:12" ht="31.8" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="5"/>
-      <c r="C62" s="31">
+      <c r="C62" s="30">
         <v>45988</v>
       </c>
-      <c r="D62" s="32"/>
+      <c r="D62" s="31"/>
       <c r="E62" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F62" s="33" t="s">
+      <c r="F62" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="G62" s="34"/>
+      <c r="G62" s="33"/>
       <c r="H62" s="12">
         <v>120</v>
       </c>
@@ -2191,17 +2194,17 @@
     <row r="63" spans="1:12" ht="31.8" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="5"/>
-      <c r="C63" s="31">
+      <c r="C63" s="30">
         <v>45988</v>
       </c>
-      <c r="D63" s="32"/>
+      <c r="D63" s="31"/>
       <c r="E63" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F63" s="33" t="s">
+      <c r="F63" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="G63" s="34"/>
+      <c r="G63" s="33"/>
       <c r="H63" s="12">
         <v>10</v>
       </c>
@@ -2215,17 +2218,17 @@
     <row r="64" spans="1:12" ht="31.8" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="5"/>
-      <c r="C64" s="31">
+      <c r="C64" s="30">
         <v>45988</v>
       </c>
-      <c r="D64" s="32"/>
+      <c r="D64" s="31"/>
       <c r="E64" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F64" s="33" t="s">
+      <c r="F64" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="G64" s="34"/>
+      <c r="G64" s="33"/>
       <c r="H64" s="12">
         <v>20</v>
       </c>
@@ -2239,17 +2242,17 @@
     <row r="65" spans="1:12" ht="31.8" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="5"/>
-      <c r="C65" s="31">
+      <c r="C65" s="30">
         <v>45988</v>
       </c>
-      <c r="D65" s="32"/>
+      <c r="D65" s="31"/>
       <c r="E65" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="33" t="s">
+      <c r="F65" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="G65" s="34"/>
+      <c r="G65" s="33"/>
       <c r="H65" s="12">
         <v>30</v>
       </c>
@@ -2263,10 +2266,10 @@
     <row r="66" spans="1:12" ht="184.8" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="5"/>
-      <c r="C66" s="31">
+      <c r="C66" s="30">
         <v>45988</v>
       </c>
-      <c r="D66" s="32"/>
+      <c r="D66" s="31"/>
       <c r="E66" s="12" t="s">
         <v>11</v>
       </c>
@@ -2287,17 +2290,17 @@
     <row r="67" spans="1:12" ht="62.4" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="5"/>
-      <c r="C67" s="31">
+      <c r="C67" s="30">
         <v>45988</v>
       </c>
-      <c r="D67" s="32"/>
+      <c r="D67" s="31"/>
       <c r="E67" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F67" s="33" t="s">
+      <c r="F67" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="G67" s="34"/>
+      <c r="G67" s="33"/>
       <c r="H67" s="12">
         <v>150</v>
       </c>
@@ -2313,17 +2316,17 @@
     <row r="68" spans="1:12" ht="31.8" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="5"/>
-      <c r="C68" s="31">
+      <c r="C68" s="30">
         <v>45988</v>
       </c>
-      <c r="D68" s="32"/>
+      <c r="D68" s="31"/>
       <c r="E68" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F68" s="33" t="s">
+      <c r="F68" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="G68" s="34"/>
+      <c r="G68" s="33"/>
       <c r="H68" s="12" t="s">
         <v>75</v>
       </c>
@@ -2337,17 +2340,17 @@
     <row r="69" spans="1:12" ht="31.8" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="5"/>
-      <c r="C69" s="31">
+      <c r="C69" s="30">
         <v>45995</v>
       </c>
-      <c r="D69" s="32"/>
+      <c r="D69" s="31"/>
       <c r="E69" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F69" s="33" t="s">
+      <c r="F69" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="G69" s="34"/>
+      <c r="G69" s="33"/>
       <c r="H69" s="12">
         <v>30</v>
       </c>
@@ -2361,17 +2364,17 @@
     <row r="70" spans="1:12" ht="31.8" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="5"/>
-      <c r="C70" s="31">
+      <c r="C70" s="30">
         <v>45995</v>
       </c>
-      <c r="D70" s="32"/>
+      <c r="D70" s="31"/>
       <c r="E70" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F70" s="33" t="s">
+      <c r="F70" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G70" s="34"/>
+      <c r="G70" s="33"/>
       <c r="H70" s="12">
         <v>100</v>
       </c>
@@ -2385,17 +2388,17 @@
     <row r="71" spans="1:12" ht="31.8" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="5"/>
-      <c r="C71" s="31">
+      <c r="C71" s="30">
         <v>45997</v>
       </c>
-      <c r="D71" s="32"/>
+      <c r="D71" s="31"/>
       <c r="E71" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F71" s="33" t="s">
+      <c r="F71" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="G71" s="34"/>
+      <c r="G71" s="33"/>
       <c r="H71" s="12">
         <v>180</v>
       </c>
@@ -2411,17 +2414,17 @@
     <row r="72" spans="1:12" ht="94.8" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="5"/>
-      <c r="C72" s="31">
+      <c r="C72" s="30">
         <v>45999</v>
       </c>
-      <c r="D72" s="32"/>
+      <c r="D72" s="31"/>
       <c r="E72" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F72" s="33" t="s">
+      <c r="F72" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="G72" s="34"/>
+      <c r="G72" s="33"/>
       <c r="H72" s="12">
         <v>180</v>
       </c>
@@ -2437,17 +2440,17 @@
     <row r="73" spans="1:12" ht="69" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="5"/>
-      <c r="C73" s="31">
+      <c r="C73" s="30">
         <v>46000</v>
       </c>
-      <c r="D73" s="32"/>
+      <c r="D73" s="31"/>
       <c r="E73" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F73" s="33" t="s">
+      <c r="F73" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="G73" s="34"/>
+      <c r="G73" s="33"/>
       <c r="H73" s="12">
         <v>180</v>
       </c>
@@ -2463,17 +2466,17 @@
     <row r="74" spans="1:12" ht="103.2" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="5"/>
-      <c r="C74" s="31">
+      <c r="C74" s="30">
         <v>46001</v>
       </c>
-      <c r="D74" s="32"/>
+      <c r="D74" s="31"/>
       <c r="E74" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F74" s="33" t="s">
+      <c r="F74" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="G74" s="34"/>
+      <c r="G74" s="33"/>
       <c r="H74" s="12">
         <v>180</v>
       </c>
@@ -2489,17 +2492,17 @@
     <row r="75" spans="1:12" ht="31.8" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="5"/>
-      <c r="C75" s="31">
+      <c r="C75" s="30">
         <v>46002</v>
       </c>
-      <c r="D75" s="32"/>
+      <c r="D75" s="31"/>
       <c r="E75" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F75" s="33" t="s">
+      <c r="F75" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="G75" s="34"/>
+      <c r="G75" s="33"/>
       <c r="H75" s="12">
         <v>30</v>
       </c>
@@ -2513,17 +2516,17 @@
     <row r="76" spans="1:12" ht="31.8" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="5"/>
-      <c r="C76" s="31">
+      <c r="C76" s="30">
         <v>46002</v>
       </c>
-      <c r="D76" s="32"/>
+      <c r="D76" s="31"/>
       <c r="E76" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F76" s="33" t="s">
+      <c r="F76" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="G76" s="34"/>
+      <c r="G76" s="33"/>
       <c r="H76" s="12">
         <v>40</v>
       </c>
@@ -2537,13 +2540,23 @@
     <row r="77" spans="1:12" ht="31.8" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="5"/>
-      <c r="C77" s="31"/>
-      <c r="D77" s="32"/>
-      <c r="E77" s="12"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="34"/>
-      <c r="H77" s="12"/>
-      <c r="I77" s="13"/>
+      <c r="C77" s="30">
+        <v>46002</v>
+      </c>
+      <c r="D77" s="31"/>
+      <c r="E77" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="G77" s="33"/>
+      <c r="H77" s="12">
+        <v>65</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>8</v>
+      </c>
       <c r="J77" s="13"/>
       <c r="K77" s="6"/>
       <c r="L77" s="1"/>
@@ -2551,11 +2564,11 @@
     <row r="78" spans="1:12" ht="31.8" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="5"/>
-      <c r="C78" s="31"/>
-      <c r="D78" s="32"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="31"/>
       <c r="E78" s="12"/>
-      <c r="F78" s="33"/>
-      <c r="G78" s="34"/>
+      <c r="F78" s="32"/>
+      <c r="G78" s="33"/>
       <c r="H78" s="12"/>
       <c r="I78" s="13"/>
       <c r="J78" s="13"/>
@@ -2565,11 +2578,11 @@
     <row r="79" spans="1:12" ht="31.8" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="5"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="32"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="31"/>
       <c r="E79" s="12"/>
-      <c r="F79" s="33"/>
-      <c r="G79" s="34"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="33"/>
       <c r="H79" s="12"/>
       <c r="I79" s="13"/>
       <c r="J79" s="13"/>
@@ -2605,11 +2618,11 @@
       <c r="L81" s="1"/>
     </row>
     <row r="82" spans="1:12" ht="24.75" customHeight="1">
-      <c r="A82" s="30"/>
-      <c r="B82" s="30"/>
-      <c r="C82" s="30"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="30"/>
+      <c r="A82" s="39"/>
+      <c r="B82" s="39"/>
+      <c r="C82" s="39"/>
+      <c r="D82" s="39"/>
+      <c r="E82" s="39"/>
       <c r="F82" s="17"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
@@ -2628,112 +2641,8 @@
     <row r="90" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="91" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="92" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="93" spans="1:12" ht="0" hidden="1" customHeight="1"/>
-    <row r="94" spans="1:12" ht="0" hidden="1" customHeight="1"/>
-    <row r="95" spans="1:12" ht="0" hidden="1" customHeight="1"/>
-    <row r="96" spans="1:12" ht="0" hidden="1" customHeight="1"/>
-    <row r="97" ht="0" hidden="1" customHeight="1"/>
   </sheetData>
   <mergeCells count="123">
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="A82:E82"/>
@@ -2758,6 +2667,105 @@
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="F39:G39"/>
     <mergeCell ref="F40:G40"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/docs/Arbeitsrapport.xlsx
+++ b/docs/Arbeitsrapport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brtoz\Codes\IPT5.1\Stundenplaner-Projekt\IPT5.1_Stundenplaner-Projekt\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sanji\Documents\GitHub\IPT5.1_Stundenplaner-Projekt\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58F376B-157A-4AA7-B131-897BDE9FD602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31CF102F-95E5-4FEA-833B-09580D2C1940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Sales Report Form" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="93">
   <si>
     <t>Datum</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>UnitTest Beschreibung</t>
+  </si>
+  <si>
+    <t>Dokumentation Plugin System beschreiben / Klassendiagramm</t>
   </si>
 </sst>
 </file>
@@ -678,6 +681,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -693,12 +699,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -723,8 +726,8 @@
       <xdr:rowOff>376521</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>2510118</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>65</xdr:row>
       <xdr:rowOff>1900520</xdr:rowOff>
     </xdr:to>
@@ -964,18 +967,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L92"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="2" width="6.88671875" customWidth="1"/>
-    <col min="3" max="3" width="3.33203125" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="37.44140625" customWidth="1"/>
-    <col min="6" max="6" width="41.5546875" customWidth="1"/>
-    <col min="7" max="7" width="3.44140625" customWidth="1"/>
+    <col min="1" max="2" width="6.85546875" customWidth="1"/>
+    <col min="3" max="3" width="3.28515625" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="37.42578125" customWidth="1"/>
+    <col min="6" max="6" width="41.5703125" customWidth="1"/>
+    <col min="7" max="7" width="3.42578125" customWidth="1"/>
     <col min="8" max="9" width="26" customWidth="1"/>
-    <col min="10" max="10" width="37.6640625" style="27" customWidth="1"/>
-    <col min="11" max="12" width="8.88671875" customWidth="1"/>
-    <col min="13" max="16384" width="12.5546875" hidden="1"/>
+    <col min="10" max="10" width="37.7109375" style="27" customWidth="1"/>
+    <col min="11" max="12" width="8.85546875" customWidth="1"/>
+    <col min="13" max="16384" width="12.5703125" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="32.25" customHeight="1">
@@ -1008,7 +1011,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" ht="107.4" customHeight="1">
+    <row r="3" spans="1:12" ht="107.45" customHeight="1">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3"/>
@@ -1040,29 +1043,29 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
     </row>
-    <row r="8" spans="1:12" ht="31.8" hidden="1" customHeight="1"/>
+    <row r="8" spans="1:12" ht="31.9" hidden="1" customHeight="1"/>
     <row r="9" spans="1:12" ht="42.6" hidden="1" customHeight="1"/>
-    <row r="10" spans="1:12" ht="31.8" hidden="1" customHeight="1"/>
+    <row r="10" spans="1:12" ht="31.9" hidden="1" customHeight="1"/>
     <row r="11" spans="1:12" ht="6" hidden="1" customHeight="1"/>
-    <row r="12" spans="1:12" ht="31.8" hidden="1" customHeight="1"/>
-    <row r="13" spans="1:12" ht="31.8" hidden="1" customHeight="1"/>
+    <row r="12" spans="1:12" ht="31.9" hidden="1" customHeight="1"/>
+    <row r="13" spans="1:12" ht="31.9" hidden="1" customHeight="1"/>
     <row r="14" spans="1:12" ht="32.25" customHeight="1"/>
     <row r="15" spans="1:12" ht="32.25" customHeight="1"/>
     <row r="16" spans="1:12" ht="37.5" customHeight="1"/>
     <row r="17" spans="1:12" ht="32.25" customHeight="1">
       <c r="A17" s="1"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="34"/>
+      <c r="D17" s="35"/>
       <c r="E17" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F17" s="34" t="s">
+      <c r="F17" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="G17" s="34"/>
+      <c r="G17" s="35"/>
       <c r="H17" s="7" t="s">
         <v>7</v>
       </c>
@@ -1078,17 +1081,17 @@
     <row r="18" spans="1:12" ht="32.25" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="35">
+      <c r="C18" s="36">
         <v>45953</v>
       </c>
-      <c r="D18" s="36"/>
+      <c r="D18" s="37"/>
       <c r="E18" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="37" t="s">
+      <c r="F18" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="38"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="8">
         <v>30</v>
       </c>
@@ -1301,7 +1304,7 @@
       <c r="K26" s="6"/>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" spans="1:12" ht="76.8" customHeight="1">
+    <row r="27" spans="1:12" ht="76.900000000000006" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="5"/>
       <c r="C27" s="30">
@@ -1327,7 +1330,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="1"/>
     </row>
-    <row r="28" spans="1:12" ht="34.200000000000003" customHeight="1">
+    <row r="28" spans="1:12" ht="34.15" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="5"/>
       <c r="C28" s="30">
@@ -1675,7 +1678,7 @@
       <c r="K41" s="6"/>
       <c r="L41" s="1"/>
     </row>
-    <row r="42" spans="1:12" ht="19.2" customHeight="1">
+    <row r="42" spans="1:12" ht="19.149999999999999" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="5"/>
       <c r="C42" s="21"/>
@@ -1691,7 +1694,7 @@
       <c r="K42" s="6"/>
       <c r="L42" s="1"/>
     </row>
-    <row r="43" spans="1:12" ht="86.4" customHeight="1">
+    <row r="43" spans="1:12" ht="86.45" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="5"/>
       <c r="C43" s="30">
@@ -1767,7 +1770,7 @@
       <c r="K45" s="6"/>
       <c r="L45" s="1"/>
     </row>
-    <row r="46" spans="1:12" ht="50.4" customHeight="1">
+    <row r="46" spans="1:12" ht="50.45" customHeight="1">
       <c r="A46" s="1"/>
       <c r="B46" s="5"/>
       <c r="C46" s="30">
@@ -1919,7 +1922,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="1"/>
     </row>
-    <row r="52" spans="1:12" ht="59.4" customHeight="1">
+    <row r="52" spans="1:12" ht="59.45" customHeight="1">
       <c r="A52" s="1"/>
       <c r="B52" s="5"/>
       <c r="C52" s="30">
@@ -2019,7 +2022,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="1"/>
     </row>
-    <row r="56" spans="1:12" ht="50.4" customHeight="1">
+    <row r="56" spans="1:12" ht="50.45" customHeight="1">
       <c r="A56" s="1"/>
       <c r="B56" s="5"/>
       <c r="C56" s="30">
@@ -2141,7 +2144,7 @@
       <c r="K60" s="6"/>
       <c r="L60" s="1"/>
     </row>
-    <row r="61" spans="1:12" ht="67.2" customHeight="1">
+    <row r="61" spans="1:12" ht="67.150000000000006" customHeight="1">
       <c r="A61" s="1"/>
       <c r="B61" s="5"/>
       <c r="C61" s="30">
@@ -2167,7 +2170,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="1"/>
     </row>
-    <row r="62" spans="1:12" ht="31.8" customHeight="1">
+    <row r="62" spans="1:12" ht="31.9" customHeight="1">
       <c r="A62" s="1"/>
       <c r="B62" s="5"/>
       <c r="C62" s="30">
@@ -2191,7 +2194,7 @@
       <c r="K62" s="6"/>
       <c r="L62" s="1"/>
     </row>
-    <row r="63" spans="1:12" ht="31.8" customHeight="1">
+    <row r="63" spans="1:12" ht="31.9" customHeight="1">
       <c r="A63" s="1"/>
       <c r="B63" s="5"/>
       <c r="C63" s="30">
@@ -2215,7 +2218,7 @@
       <c r="K63" s="6"/>
       <c r="L63" s="1"/>
     </row>
-    <row r="64" spans="1:12" ht="31.8" customHeight="1">
+    <row r="64" spans="1:12" ht="31.9" customHeight="1">
       <c r="A64" s="1"/>
       <c r="B64" s="5"/>
       <c r="C64" s="30">
@@ -2239,7 +2242,7 @@
       <c r="K64" s="6"/>
       <c r="L64" s="1"/>
     </row>
-    <row r="65" spans="1:12" ht="31.8" customHeight="1">
+    <row r="65" spans="1:12" ht="31.9" customHeight="1">
       <c r="A65" s="1"/>
       <c r="B65" s="5"/>
       <c r="C65" s="30">
@@ -2263,7 +2266,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="1"/>
     </row>
-    <row r="66" spans="1:12" ht="184.8" customHeight="1">
+    <row r="66" spans="1:12" ht="184.9" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="5"/>
       <c r="C66" s="30">
@@ -2287,7 +2290,7 @@
       <c r="K66" s="6"/>
       <c r="L66" s="1"/>
     </row>
-    <row r="67" spans="1:12" ht="62.4" customHeight="1">
+    <row r="67" spans="1:12" ht="62.45" customHeight="1">
       <c r="A67" s="1"/>
       <c r="B67" s="5"/>
       <c r="C67" s="30">
@@ -2313,7 +2316,7 @@
       <c r="K67" s="6"/>
       <c r="L67" s="1"/>
     </row>
-    <row r="68" spans="1:12" ht="31.8" customHeight="1">
+    <row r="68" spans="1:12" ht="31.9" customHeight="1">
       <c r="A68" s="1"/>
       <c r="B68" s="5"/>
       <c r="C68" s="30">
@@ -2337,7 +2340,7 @@
       <c r="K68" s="6"/>
       <c r="L68" s="1"/>
     </row>
-    <row r="69" spans="1:12" ht="31.8" customHeight="1">
+    <row r="69" spans="1:12" ht="31.9" customHeight="1">
       <c r="A69" s="1"/>
       <c r="B69" s="5"/>
       <c r="C69" s="30">
@@ -2361,7 +2364,7 @@
       <c r="K69" s="6"/>
       <c r="L69" s="1"/>
     </row>
-    <row r="70" spans="1:12" ht="31.8" customHeight="1">
+    <row r="70" spans="1:12" ht="31.9" customHeight="1">
       <c r="A70" s="1"/>
       <c r="B70" s="5"/>
       <c r="C70" s="30">
@@ -2385,7 +2388,7 @@
       <c r="K70" s="6"/>
       <c r="L70" s="1"/>
     </row>
-    <row r="71" spans="1:12" ht="31.8" customHeight="1">
+    <row r="71" spans="1:12" ht="31.9" customHeight="1">
       <c r="A71" s="1"/>
       <c r="B71" s="5"/>
       <c r="C71" s="30">
@@ -2411,7 +2414,7 @@
       <c r="K71" s="6"/>
       <c r="L71" s="1"/>
     </row>
-    <row r="72" spans="1:12" ht="94.8" customHeight="1">
+    <row r="72" spans="1:12" ht="94.9" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="5"/>
       <c r="C72" s="30">
@@ -2463,7 +2466,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" spans="1:12" ht="103.2" customHeight="1">
+    <row r="74" spans="1:12" ht="103.15" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="5"/>
       <c r="C74" s="30">
@@ -2489,7 +2492,7 @@
       <c r="K74" s="6"/>
       <c r="L74" s="1"/>
     </row>
-    <row r="75" spans="1:12" ht="31.8" customHeight="1">
+    <row r="75" spans="1:12" ht="31.9" customHeight="1">
       <c r="A75" s="1"/>
       <c r="B75" s="5"/>
       <c r="C75" s="30">
@@ -2513,7 +2516,7 @@
       <c r="K75" s="6"/>
       <c r="L75" s="1"/>
     </row>
-    <row r="76" spans="1:12" ht="31.8" customHeight="1">
+    <row r="76" spans="1:12" ht="31.9" customHeight="1">
       <c r="A76" s="1"/>
       <c r="B76" s="5"/>
       <c r="C76" s="30">
@@ -2537,7 +2540,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="1"/>
     </row>
-    <row r="77" spans="1:12" ht="31.8" customHeight="1">
+    <row r="77" spans="1:12" ht="31.9" customHeight="1">
       <c r="A77" s="1"/>
       <c r="B77" s="5"/>
       <c r="C77" s="30">
@@ -2561,21 +2564,31 @@
       <c r="K77" s="6"/>
       <c r="L77" s="1"/>
     </row>
-    <row r="78" spans="1:12" ht="31.8" customHeight="1">
+    <row r="78" spans="1:12" ht="31.9" customHeight="1">
       <c r="A78" s="1"/>
       <c r="B78" s="5"/>
-      <c r="C78" s="30"/>
+      <c r="C78" s="30">
+        <v>46002</v>
+      </c>
       <c r="D78" s="31"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="32"/>
+      <c r="E78" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F78" s="32" t="s">
+        <v>92</v>
+      </c>
       <c r="G78" s="33"/>
-      <c r="H78" s="12"/>
-      <c r="I78" s="13"/>
+      <c r="H78" s="12">
+        <v>30</v>
+      </c>
+      <c r="I78" s="13" t="s">
+        <v>8</v>
+      </c>
       <c r="J78" s="13"/>
       <c r="K78" s="6"/>
       <c r="L78" s="1"/>
     </row>
-    <row r="79" spans="1:12" ht="31.8" customHeight="1">
+    <row r="79" spans="1:12" ht="31.9" customHeight="1">
       <c r="A79" s="1"/>
       <c r="B79" s="5"/>
       <c r="C79" s="30"/>
@@ -2618,11 +2631,11 @@
       <c r="L81" s="1"/>
     </row>
     <row r="82" spans="1:12" ht="24.75" customHeight="1">
-      <c r="A82" s="39"/>
-      <c r="B82" s="39"/>
-      <c r="C82" s="39"/>
-      <c r="D82" s="39"/>
-      <c r="E82" s="39"/>
+      <c r="A82" s="34"/>
+      <c r="B82" s="34"/>
+      <c r="C82" s="34"/>
+      <c r="D82" s="34"/>
+      <c r="E82" s="34"/>
       <c r="F82" s="17"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
@@ -2643,6 +2656,105 @@
     <row r="92" spans="1:12" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="123">
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="A82:E82"/>
@@ -2667,105 +2779,6 @@
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="F39:G39"/>
     <mergeCell ref="F40:G40"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="C56:D56"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="F68:G68"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
